--- a/resultados/telemacoborba/erros_varredura.xlsx
+++ b/resultados/telemacoborba/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1469"/>
+  <dimension ref="A1:F1475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41552,6 +41552,174 @@
         </is>
       </c>
     </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/servicos/guia-de-servicos/obituario/18604-falecimentos-do-dia-16-06-2023?tmpl=component&amp;print=1</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>HTTP_520</t>
+        </is>
+      </c>
+      <c r="D1470" t="n">
+        <v>520</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1470" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:58:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/servicos/guia-de-servicos/obituario/18604-falecimentos-do-dia-16-06-2023?tmpl=component&amp;print=1</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>HTTP_521</t>
+        </is>
+      </c>
+      <c r="D1471" t="n">
+        <v>521</v>
+      </c>
+      <c r="E1471" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1471" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:58:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/component/mailto/?tmpl=component&amp;template=cloudbase3&amp;link=dea2b9deafd401109e04b1e472155f13b66d1c31</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>HTTP_521</t>
+        </is>
+      </c>
+      <c r="D1472" t="n">
+        <v>521</v>
+      </c>
+      <c r="E1472" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1472" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:58:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/component/mailto/?tmpl=component&amp;template=cloudbase3&amp;link=dea2b9deafd401109e04b1e472155f13b66d1c31</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>HTTP_521</t>
+        </is>
+      </c>
+      <c r="D1473" t="n">
+        <v>521</v>
+      </c>
+      <c r="E1473" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1473" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:58:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/servicos/guia-de-servicos/obituario/18601-falecimentos-do-dia-13-06-2023?tmpl=component&amp;print=1</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>HTTP_521</t>
+        </is>
+      </c>
+      <c r="D1474" t="n">
+        <v>521</v>
+      </c>
+      <c r="E1474" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1474" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:58:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/servicos/guia-de-servicos/obituario/18601-falecimentos-do-dia-13-06-2023?tmpl=component&amp;print=1</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D1475" t="n">
+        <v>502</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1475" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:59:03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/telemacoborba/erros_varredura.xlsx
+++ b/resultados/telemacoborba/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1475"/>
+  <dimension ref="A1:F1477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36245,7 +36245,7 @@
       </c>
       <c r="C1280" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D1280" t="n">
@@ -36256,7 +36256,7 @@
       </c>
       <c r="F1280" t="inlineStr">
         <is>
-          <t>2026-08-04 23:07:02</t>
+          <t>2026-08-04 23:09:03</t>
         </is>
       </c>
     </row>
@@ -36268,23 +36268,23 @@
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>https://telemacoborba.pr.gov.br/melhoramigo</t>
+          <t>https://telemacoborba.pr.gov.br/equipe</t>
         </is>
       </c>
       <c r="C1281" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D1281" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E1281" t="n">
         <v>3</v>
       </c>
       <c r="F1281" t="inlineStr">
         <is>
-          <t>2026-08-04 23:09:03</t>
+          <t>2026-08-04 23:10:07</t>
         </is>
       </c>
     </row>
@@ -36312,7 +36312,7 @@
       </c>
       <c r="F1282" t="inlineStr">
         <is>
-          <t>2026-08-04 23:10:07</t>
+          <t>2026-08-04 23:10:13</t>
         </is>
       </c>
     </row>
@@ -36324,7 +36324,7 @@
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>https://telemacoborba.pr.gov.br/equipe</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/18552-saude-disponibiliza-checklist-online-para-prevencao-e-cuidados-contra-a-dengue?tmpl=component&amp;print=1&amp;layout=default</t>
         </is>
       </c>
       <c r="C1283" t="inlineStr">
@@ -36340,7 +36340,7 @@
       </c>
       <c r="F1283" t="inlineStr">
         <is>
-          <t>2026-08-04 23:10:13</t>
+          <t>2026-08-04 23:10:17</t>
         </is>
       </c>
     </row>
@@ -36368,7 +36368,7 @@
       </c>
       <c r="F1284" t="inlineStr">
         <is>
-          <t>2026-08-04 23:10:17</t>
+          <t>2026-08-04 23:10:22</t>
         </is>
       </c>
     </row>
@@ -36380,7 +36380,7 @@
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/18552-saude-disponibiliza-checklist-online-para-prevencao-e-cuidados-contra-a-dengue?tmpl=component&amp;print=1&amp;layout=default</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/component/mailto/?tmpl=component&amp;template=cloudbase3&amp;link=afd797afbc64ac946d44f973d7b39bc67899e46d</t>
         </is>
       </c>
       <c r="C1285" t="inlineStr">
@@ -36424,7 +36424,7 @@
       </c>
       <c r="F1286" t="inlineStr">
         <is>
-          <t>2026-08-04 23:10:22</t>
+          <t>2026-08-04 23:10:27</t>
         </is>
       </c>
     </row>
@@ -36436,7 +36436,7 @@
       </c>
       <c r="B1287" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/component/mailto/?tmpl=component&amp;template=cloudbase3&amp;link=afd797afbc64ac946d44f973d7b39bc67899e46d</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/18573-telemaco-borba-registra-52-casos-positivos-de-dengue</t>
         </is>
       </c>
       <c r="C1287" t="inlineStr">
@@ -36452,7 +36452,7 @@
       </c>
       <c r="F1287" t="inlineStr">
         <is>
-          <t>2026-08-04 23:10:27</t>
+          <t>2026-08-04 23:10:28</t>
         </is>
       </c>
     </row>
@@ -36480,7 +36480,7 @@
       </c>
       <c r="F1288" t="inlineStr">
         <is>
-          <t>2026-08-04 23:10:28</t>
+          <t>2026-08-04 23:10:33</t>
         </is>
       </c>
     </row>
@@ -36492,7 +36492,7 @@
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/18573-telemaco-borba-registra-52-casos-positivos-de-dengue</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/18545-saude-realiza-repescagem-de-vacinacao-contra-a-covid-19-e-gripe-no-domingo-18</t>
         </is>
       </c>
       <c r="C1289" t="inlineStr">
@@ -36508,7 +36508,7 @@
       </c>
       <c r="F1289" t="inlineStr">
         <is>
-          <t>2026-08-04 23:10:33</t>
+          <t>2026-08-04 23:10:34</t>
         </is>
       </c>
     </row>
@@ -36536,7 +36536,7 @@
       </c>
       <c r="F1290" t="inlineStr">
         <is>
-          <t>2026-08-04 23:10:34</t>
+          <t>2026-08-04 23:10:40</t>
         </is>
       </c>
     </row>
@@ -36548,7 +36548,7 @@
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/18545-saude-realiza-repescagem-de-vacinacao-contra-a-covid-19-e-gripe-no-domingo-18</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23513-edicao-2837</t>
         </is>
       </c>
       <c r="C1291" t="inlineStr">
@@ -36560,11 +36560,11 @@
         <v>404</v>
       </c>
       <c r="E1291" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1291" t="inlineStr">
         <is>
-          <t>2026-08-04 23:10:40</t>
+          <t>2026-08-04 23:11:11</t>
         </is>
       </c>
     </row>
@@ -36592,7 +36592,7 @@
       </c>
       <c r="F1292" t="inlineStr">
         <is>
-          <t>2026-08-04 23:11:11</t>
+          <t>2026-08-04 23:11:16</t>
         </is>
       </c>
     </row>
@@ -36604,7 +36604,7 @@
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23513-edicao-2837</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23507-edicao-2836</t>
         </is>
       </c>
       <c r="C1293" t="inlineStr">
@@ -36620,7 +36620,7 @@
       </c>
       <c r="F1293" t="inlineStr">
         <is>
-          <t>2026-08-04 23:11:16</t>
+          <t>2026-08-04 23:11:17</t>
         </is>
       </c>
     </row>
@@ -36648,7 +36648,7 @@
       </c>
       <c r="F1294" t="inlineStr">
         <is>
-          <t>2026-08-04 23:11:17</t>
+          <t>2026-08-04 23:11:22</t>
         </is>
       </c>
     </row>
@@ -36660,7 +36660,7 @@
       </c>
       <c r="B1295" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23507-edicao-2836</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23502-edicao-2835</t>
         </is>
       </c>
       <c r="C1295" t="inlineStr">
@@ -36704,7 +36704,7 @@
       </c>
       <c r="F1296" t="inlineStr">
         <is>
-          <t>2026-08-04 23:11:22</t>
+          <t>2026-08-04 23:11:27</t>
         </is>
       </c>
     </row>
@@ -36716,7 +36716,7 @@
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23502-edicao-2835</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23489-edicao-2834-complementar-2</t>
         </is>
       </c>
       <c r="C1297" t="inlineStr">
@@ -36732,7 +36732,7 @@
       </c>
       <c r="F1297" t="inlineStr">
         <is>
-          <t>2026-08-04 23:11:27</t>
+          <t>2026-08-04 23:11:28</t>
         </is>
       </c>
     </row>
@@ -36760,7 +36760,7 @@
       </c>
       <c r="F1298" t="inlineStr">
         <is>
-          <t>2026-08-04 23:11:28</t>
+          <t>2026-08-04 23:11:33</t>
         </is>
       </c>
     </row>
@@ -36772,7 +36772,7 @@
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23489-edicao-2834-complementar-2</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23488-edicao-2834-complementar-1</t>
         </is>
       </c>
       <c r="C1299" t="inlineStr">
@@ -36816,7 +36816,7 @@
       </c>
       <c r="F1300" t="inlineStr">
         <is>
-          <t>2026-08-04 23:11:33</t>
+          <t>2026-08-04 23:11:38</t>
         </is>
       </c>
     </row>
@@ -36828,7 +36828,7 @@
       </c>
       <c r="B1301" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23488-edicao-2834-complementar-1</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23487-edicao-2834</t>
         </is>
       </c>
       <c r="C1301" t="inlineStr">
@@ -36844,7 +36844,7 @@
       </c>
       <c r="F1301" t="inlineStr">
         <is>
-          <t>2026-08-04 23:11:38</t>
+          <t>2026-08-04 23:11:39</t>
         </is>
       </c>
     </row>
@@ -36872,7 +36872,7 @@
       </c>
       <c r="F1302" t="inlineStr">
         <is>
-          <t>2026-08-04 23:11:39</t>
+          <t>2026-08-04 23:11:44</t>
         </is>
       </c>
     </row>
@@ -36884,7 +36884,7 @@
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23487-edicao-2834</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23481-edicao-2833</t>
         </is>
       </c>
       <c r="C1303" t="inlineStr">
@@ -36900,7 +36900,7 @@
       </c>
       <c r="F1303" t="inlineStr">
         <is>
-          <t>2026-08-04 23:11:44</t>
+          <t>2026-08-04 23:11:45</t>
         </is>
       </c>
     </row>
@@ -36928,7 +36928,7 @@
       </c>
       <c r="F1304" t="inlineStr">
         <is>
-          <t>2026-08-04 23:11:45</t>
+          <t>2026-08-04 23:11:49</t>
         </is>
       </c>
     </row>
@@ -36940,7 +36940,7 @@
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23481-edicao-2833</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23476-edicao-2832</t>
         </is>
       </c>
       <c r="C1305" t="inlineStr">
@@ -36956,7 +36956,7 @@
       </c>
       <c r="F1305" t="inlineStr">
         <is>
-          <t>2026-08-04 23:11:49</t>
+          <t>2026-08-04 23:11:50</t>
         </is>
       </c>
     </row>
@@ -36984,7 +36984,7 @@
       </c>
       <c r="F1306" t="inlineStr">
         <is>
-          <t>2026-08-04 23:11:50</t>
+          <t>2026-08-04 23:11:55</t>
         </is>
       </c>
     </row>
@@ -36996,7 +36996,7 @@
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23476-edicao-2832</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23470-edicao-2831</t>
         </is>
       </c>
       <c r="C1307" t="inlineStr">
@@ -37040,7 +37040,7 @@
       </c>
       <c r="F1308" t="inlineStr">
         <is>
-          <t>2026-08-04 23:11:55</t>
+          <t>2026-08-04 23:12:00</t>
         </is>
       </c>
     </row>
@@ -37052,7 +37052,7 @@
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23470-edicao-2831</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23467-edicao-2830</t>
         </is>
       </c>
       <c r="C1309" t="inlineStr">
@@ -37068,7 +37068,7 @@
       </c>
       <c r="F1309" t="inlineStr">
         <is>
-          <t>2026-08-04 23:12:00</t>
+          <t>2026-08-04 23:12:01</t>
         </is>
       </c>
     </row>
@@ -37096,7 +37096,7 @@
       </c>
       <c r="F1310" t="inlineStr">
         <is>
-          <t>2026-08-04 23:12:01</t>
+          <t>2026-08-04 23:12:06</t>
         </is>
       </c>
     </row>
@@ -37108,7 +37108,7 @@
       </c>
       <c r="B1311" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23467-edicao-2830</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23461-edicao-2829</t>
         </is>
       </c>
       <c r="C1311" t="inlineStr">
@@ -37124,7 +37124,7 @@
       </c>
       <c r="F1311" t="inlineStr">
         <is>
-          <t>2026-08-04 23:12:06</t>
+          <t>2026-08-04 23:12:07</t>
         </is>
       </c>
     </row>
@@ -37152,7 +37152,7 @@
       </c>
       <c r="F1312" t="inlineStr">
         <is>
-          <t>2026-08-04 23:12:07</t>
+          <t>2026-08-04 23:12:12</t>
         </is>
       </c>
     </row>
@@ -37164,7 +37164,7 @@
       </c>
       <c r="B1313" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23461-edicao-2829</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23457-edicao-2828</t>
         </is>
       </c>
       <c r="C1313" t="inlineStr">
@@ -37208,7 +37208,7 @@
       </c>
       <c r="F1314" t="inlineStr">
         <is>
-          <t>2026-08-04 23:12:12</t>
+          <t>2026-08-04 23:12:17</t>
         </is>
       </c>
     </row>
@@ -37220,7 +37220,7 @@
       </c>
       <c r="B1315" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23457-edicao-2828</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23453-edicao-2827</t>
         </is>
       </c>
       <c r="C1315" t="inlineStr">
@@ -37236,7 +37236,7 @@
       </c>
       <c r="F1315" t="inlineStr">
         <is>
-          <t>2026-08-04 23:12:17</t>
+          <t>2026-08-04 23:12:18</t>
         </is>
       </c>
     </row>
@@ -37264,7 +37264,7 @@
       </c>
       <c r="F1316" t="inlineStr">
         <is>
-          <t>2026-08-04 23:12:18</t>
+          <t>2026-08-04 23:12:23</t>
         </is>
       </c>
     </row>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="B1317" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23453-edicao-2827</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23448-edicao-2826</t>
         </is>
       </c>
       <c r="C1317" t="inlineStr">
@@ -37320,7 +37320,7 @@
       </c>
       <c r="F1318" t="inlineStr">
         <is>
-          <t>2026-08-04 23:12:23</t>
+          <t>2026-08-04 23:12:28</t>
         </is>
       </c>
     </row>
@@ -37332,7 +37332,7 @@
       </c>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23448-edicao-2826</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23442-edicao-2825</t>
         </is>
       </c>
       <c r="C1319" t="inlineStr">
@@ -37348,7 +37348,7 @@
       </c>
       <c r="F1319" t="inlineStr">
         <is>
-          <t>2026-08-04 23:12:28</t>
+          <t>2026-08-04 23:12:29</t>
         </is>
       </c>
     </row>
@@ -37376,7 +37376,7 @@
       </c>
       <c r="F1320" t="inlineStr">
         <is>
-          <t>2026-08-04 23:12:29</t>
+          <t>2026-08-04 23:12:34</t>
         </is>
       </c>
     </row>
@@ -37388,7 +37388,7 @@
       </c>
       <c r="B1321" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23442-edicao-2825</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23438-edicao-2824</t>
         </is>
       </c>
       <c r="C1321" t="inlineStr">
@@ -37432,7 +37432,7 @@
       </c>
       <c r="F1322" t="inlineStr">
         <is>
-          <t>2026-08-04 23:12:34</t>
+          <t>2026-08-04 23:12:39</t>
         </is>
       </c>
     </row>
@@ -37444,7 +37444,7 @@
       </c>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23438-edicao-2824</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23429-edicao-2823</t>
         </is>
       </c>
       <c r="C1323" t="inlineStr">
@@ -37460,7 +37460,7 @@
       </c>
       <c r="F1323" t="inlineStr">
         <is>
-          <t>2026-08-04 23:12:39</t>
+          <t>2026-08-04 23:12:40</t>
         </is>
       </c>
     </row>
@@ -37488,7 +37488,7 @@
       </c>
       <c r="F1324" t="inlineStr">
         <is>
-          <t>2026-08-04 23:12:40</t>
+          <t>2026-08-04 23:12:45</t>
         </is>
       </c>
     </row>
@@ -37500,7 +37500,7 @@
       </c>
       <c r="B1325" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23429-edicao-2823</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23423-edicao-2822</t>
         </is>
       </c>
       <c r="C1325" t="inlineStr">
@@ -37516,7 +37516,7 @@
       </c>
       <c r="F1325" t="inlineStr">
         <is>
-          <t>2026-08-04 23:12:45</t>
+          <t>2026-08-04 23:12:46</t>
         </is>
       </c>
     </row>
@@ -37544,7 +37544,7 @@
       </c>
       <c r="F1326" t="inlineStr">
         <is>
-          <t>2026-08-04 23:12:46</t>
+          <t>2026-08-04 23:12:51</t>
         </is>
       </c>
     </row>
@@ -37556,7 +37556,7 @@
       </c>
       <c r="B1327" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23423-edicao-2822</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23419-edicao-2821</t>
         </is>
       </c>
       <c r="C1327" t="inlineStr">
@@ -37600,7 +37600,7 @@
       </c>
       <c r="F1328" t="inlineStr">
         <is>
-          <t>2026-08-04 23:12:51</t>
+          <t>2026-08-04 23:12:56</t>
         </is>
       </c>
     </row>
@@ -37612,7 +37612,7 @@
       </c>
       <c r="B1329" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23419-edicao-2821</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23415-edicao-2820-complementar</t>
         </is>
       </c>
       <c r="C1329" t="inlineStr">
@@ -37628,7 +37628,7 @@
       </c>
       <c r="F1329" t="inlineStr">
         <is>
-          <t>2026-08-04 23:12:56</t>
+          <t>2026-08-04 23:12:57</t>
         </is>
       </c>
     </row>
@@ -37656,7 +37656,7 @@
       </c>
       <c r="F1330" t="inlineStr">
         <is>
-          <t>2026-08-04 23:12:57</t>
+          <t>2026-08-04 23:13:02</t>
         </is>
       </c>
     </row>
@@ -37668,7 +37668,7 @@
       </c>
       <c r="B1331" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23415-edicao-2820-complementar</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23414-edicao-2820</t>
         </is>
       </c>
       <c r="C1331" t="inlineStr">
@@ -37712,7 +37712,7 @@
       </c>
       <c r="F1332" t="inlineStr">
         <is>
-          <t>2026-08-04 23:13:02</t>
+          <t>2026-08-04 23:13:07</t>
         </is>
       </c>
     </row>
@@ -37724,7 +37724,7 @@
       </c>
       <c r="B1333" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23414-edicao-2820</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23412-edicao-2819</t>
         </is>
       </c>
       <c r="C1333" t="inlineStr">
@@ -37740,7 +37740,7 @@
       </c>
       <c r="F1333" t="inlineStr">
         <is>
-          <t>2026-08-04 23:13:07</t>
+          <t>2026-08-04 23:13:08</t>
         </is>
       </c>
     </row>
@@ -37768,7 +37768,7 @@
       </c>
       <c r="F1334" t="inlineStr">
         <is>
-          <t>2026-08-04 23:13:08</t>
+          <t>2026-08-04 23:13:13</t>
         </is>
       </c>
     </row>
@@ -37780,7 +37780,7 @@
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23412-edicao-2819</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23405-edicao-2818</t>
         </is>
       </c>
       <c r="C1335" t="inlineStr">
@@ -37824,7 +37824,7 @@
       </c>
       <c r="F1336" t="inlineStr">
         <is>
-          <t>2026-08-04 23:13:13</t>
+          <t>2026-08-04 23:13:18</t>
         </is>
       </c>
     </row>
@@ -37836,7 +37836,7 @@
       </c>
       <c r="B1337" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23405-edicao-2818</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23402-edicao-2817</t>
         </is>
       </c>
       <c r="C1337" t="inlineStr">
@@ -37852,7 +37852,7 @@
       </c>
       <c r="F1337" t="inlineStr">
         <is>
-          <t>2026-08-04 23:13:18</t>
+          <t>2026-08-04 23:13:19</t>
         </is>
       </c>
     </row>
@@ -37880,7 +37880,7 @@
       </c>
       <c r="F1338" t="inlineStr">
         <is>
-          <t>2026-08-04 23:13:19</t>
+          <t>2026-08-04 23:13:24</t>
         </is>
       </c>
     </row>
@@ -37892,7 +37892,7 @@
       </c>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23402-edicao-2817</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23396-edicao-2816</t>
         </is>
       </c>
       <c r="C1339" t="inlineStr">
@@ -37936,7 +37936,7 @@
       </c>
       <c r="F1340" t="inlineStr">
         <is>
-          <t>2026-08-04 23:13:24</t>
+          <t>2026-08-04 23:13:29</t>
         </is>
       </c>
     </row>
@@ -37948,7 +37948,7 @@
       </c>
       <c r="B1341" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23396-edicao-2816</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23392-edicao-2815</t>
         </is>
       </c>
       <c r="C1341" t="inlineStr">
@@ -37964,7 +37964,7 @@
       </c>
       <c r="F1341" t="inlineStr">
         <is>
-          <t>2026-08-04 23:13:29</t>
+          <t>2026-08-04 23:13:30</t>
         </is>
       </c>
     </row>
@@ -37992,7 +37992,7 @@
       </c>
       <c r="F1342" t="inlineStr">
         <is>
-          <t>2026-08-04 23:13:30</t>
+          <t>2026-08-04 23:13:35</t>
         </is>
       </c>
     </row>
@@ -38004,7 +38004,7 @@
       </c>
       <c r="B1343" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23392-edicao-2815</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23389-edicao-2814</t>
         </is>
       </c>
       <c r="C1343" t="inlineStr">
@@ -38048,7 +38048,7 @@
       </c>
       <c r="F1344" t="inlineStr">
         <is>
-          <t>2026-08-04 23:13:35</t>
+          <t>2026-08-04 23:13:40</t>
         </is>
       </c>
     </row>
@@ -38060,7 +38060,7 @@
       </c>
       <c r="B1345" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23389-edicao-2814</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23387-edicao-2813</t>
         </is>
       </c>
       <c r="C1345" t="inlineStr">
@@ -38076,7 +38076,7 @@
       </c>
       <c r="F1345" t="inlineStr">
         <is>
-          <t>2026-08-04 23:13:40</t>
+          <t>2026-08-04 23:13:41</t>
         </is>
       </c>
     </row>
@@ -38104,7 +38104,7 @@
       </c>
       <c r="F1346" t="inlineStr">
         <is>
-          <t>2026-08-04 23:13:41</t>
+          <t>2026-08-04 23:13:46</t>
         </is>
       </c>
     </row>
@@ -38116,7 +38116,7 @@
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23387-edicao-2813</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23362-edicao-2812</t>
         </is>
       </c>
       <c r="C1347" t="inlineStr">
@@ -38160,7 +38160,7 @@
       </c>
       <c r="F1348" t="inlineStr">
         <is>
-          <t>2026-08-04 23:13:46</t>
+          <t>2026-08-04 23:13:51</t>
         </is>
       </c>
     </row>
@@ -38172,7 +38172,7 @@
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23362-edicao-2812</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23357-edicao-2811</t>
         </is>
       </c>
       <c r="C1349" t="inlineStr">
@@ -38188,7 +38188,7 @@
       </c>
       <c r="F1349" t="inlineStr">
         <is>
-          <t>2026-08-04 23:13:51</t>
+          <t>2026-08-04 23:13:52</t>
         </is>
       </c>
     </row>
@@ -38216,7 +38216,7 @@
       </c>
       <c r="F1350" t="inlineStr">
         <is>
-          <t>2026-08-04 23:13:52</t>
+          <t>2026-08-04 23:13:57</t>
         </is>
       </c>
     </row>
@@ -38228,7 +38228,7 @@
       </c>
       <c r="B1351" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23357-edicao-2811</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23345-edicao-2810</t>
         </is>
       </c>
       <c r="C1351" t="inlineStr">
@@ -38272,7 +38272,7 @@
       </c>
       <c r="F1352" t="inlineStr">
         <is>
-          <t>2026-08-04 23:13:57</t>
+          <t>2026-08-04 23:14:02</t>
         </is>
       </c>
     </row>
@@ -38284,7 +38284,7 @@
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23345-edicao-2810</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23337-edicao-2809</t>
         </is>
       </c>
       <c r="C1353" t="inlineStr">
@@ -38300,7 +38300,7 @@
       </c>
       <c r="F1353" t="inlineStr">
         <is>
-          <t>2026-08-04 23:14:02</t>
+          <t>2026-08-04 23:14:03</t>
         </is>
       </c>
     </row>
@@ -38328,7 +38328,7 @@
       </c>
       <c r="F1354" t="inlineStr">
         <is>
-          <t>2026-08-04 23:14:03</t>
+          <t>2026-08-04 23:14:08</t>
         </is>
       </c>
     </row>
@@ -38340,7 +38340,7 @@
       </c>
       <c r="B1355" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23337-edicao-2809</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23328-edicao-2808</t>
         </is>
       </c>
       <c r="C1355" t="inlineStr">
@@ -38356,7 +38356,7 @@
       </c>
       <c r="F1355" t="inlineStr">
         <is>
-          <t>2026-08-04 23:14:08</t>
+          <t>2026-08-04 23:14:09</t>
         </is>
       </c>
     </row>
@@ -38384,7 +38384,7 @@
       </c>
       <c r="F1356" t="inlineStr">
         <is>
-          <t>2026-08-04 23:14:09</t>
+          <t>2026-08-04 23:14:14</t>
         </is>
       </c>
     </row>
@@ -38396,7 +38396,7 @@
       </c>
       <c r="B1357" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23328-edicao-2808</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23324-edicao-2807</t>
         </is>
       </c>
       <c r="C1357" t="inlineStr">
@@ -38440,7 +38440,7 @@
       </c>
       <c r="F1358" t="inlineStr">
         <is>
-          <t>2026-08-04 23:14:14</t>
+          <t>2026-08-04 23:14:19</t>
         </is>
       </c>
     </row>
@@ -38452,7 +38452,7 @@
       </c>
       <c r="B1359" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23324-edicao-2807</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23320-edicao-2806</t>
         </is>
       </c>
       <c r="C1359" t="inlineStr">
@@ -38468,7 +38468,7 @@
       </c>
       <c r="F1359" t="inlineStr">
         <is>
-          <t>2026-08-04 23:14:19</t>
+          <t>2026-08-04 23:14:20</t>
         </is>
       </c>
     </row>
@@ -38496,7 +38496,7 @@
       </c>
       <c r="F1360" t="inlineStr">
         <is>
-          <t>2026-08-04 23:14:20</t>
+          <t>2026-08-04 23:14:25</t>
         </is>
       </c>
     </row>
@@ -38508,7 +38508,7 @@
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23320-edicao-2806</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23312-edicao-2805</t>
         </is>
       </c>
       <c r="C1361" t="inlineStr">
@@ -38552,7 +38552,7 @@
       </c>
       <c r="F1362" t="inlineStr">
         <is>
-          <t>2026-08-04 23:14:25</t>
+          <t>2026-08-04 23:14:30</t>
         </is>
       </c>
     </row>
@@ -38564,7 +38564,7 @@
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23312-edicao-2805</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23307-edicao-2804</t>
         </is>
       </c>
       <c r="C1363" t="inlineStr">
@@ -38580,7 +38580,7 @@
       </c>
       <c r="F1363" t="inlineStr">
         <is>
-          <t>2026-08-04 23:14:30</t>
+          <t>2026-08-04 23:14:31</t>
         </is>
       </c>
     </row>
@@ -38608,7 +38608,7 @@
       </c>
       <c r="F1364" t="inlineStr">
         <is>
-          <t>2026-08-04 23:14:31</t>
+          <t>2026-08-04 23:14:36</t>
         </is>
       </c>
     </row>
@@ -38620,7 +38620,7 @@
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23307-edicao-2804</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23304-edicao-2803</t>
         </is>
       </c>
       <c r="C1365" t="inlineStr">
@@ -38636,7 +38636,7 @@
       </c>
       <c r="F1365" t="inlineStr">
         <is>
-          <t>2026-08-04 23:14:36</t>
+          <t>2026-08-04 23:14:37</t>
         </is>
       </c>
     </row>
@@ -38664,7 +38664,7 @@
       </c>
       <c r="F1366" t="inlineStr">
         <is>
-          <t>2026-08-04 23:14:37</t>
+          <t>2026-08-04 23:14:42</t>
         </is>
       </c>
     </row>
@@ -38676,7 +38676,7 @@
       </c>
       <c r="B1367" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23304-edicao-2803</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23293-edicao-2802</t>
         </is>
       </c>
       <c r="C1367" t="inlineStr">
@@ -38720,7 +38720,7 @@
       </c>
       <c r="F1368" t="inlineStr">
         <is>
-          <t>2026-08-04 23:14:42</t>
+          <t>2026-08-04 23:14:47</t>
         </is>
       </c>
     </row>
@@ -38732,7 +38732,7 @@
       </c>
       <c r="B1369" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23293-edicao-2802</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23285-edicao-2801</t>
         </is>
       </c>
       <c r="C1369" t="inlineStr">
@@ -38748,7 +38748,7 @@
       </c>
       <c r="F1369" t="inlineStr">
         <is>
-          <t>2026-08-04 23:14:47</t>
+          <t>2026-08-04 23:14:48</t>
         </is>
       </c>
     </row>
@@ -38776,7 +38776,7 @@
       </c>
       <c r="F1370" t="inlineStr">
         <is>
-          <t>2026-08-04 23:14:48</t>
+          <t>2026-08-04 23:14:53</t>
         </is>
       </c>
     </row>
@@ -38788,7 +38788,7 @@
       </c>
       <c r="B1371" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23285-edicao-2801</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23280-edicao-2800</t>
         </is>
       </c>
       <c r="C1371" t="inlineStr">
@@ -38804,7 +38804,7 @@
       </c>
       <c r="F1371" t="inlineStr">
         <is>
-          <t>2026-08-04 23:14:53</t>
+          <t>2026-08-04 23:14:54</t>
         </is>
       </c>
     </row>
@@ -38832,7 +38832,7 @@
       </c>
       <c r="F1372" t="inlineStr">
         <is>
-          <t>2026-08-04 23:14:54</t>
+          <t>2026-08-04 23:14:59</t>
         </is>
       </c>
     </row>
@@ -38844,7 +38844,7 @@
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23280-edicao-2800</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23277-edicao-2799</t>
         </is>
       </c>
       <c r="C1373" t="inlineStr">
@@ -38888,7 +38888,7 @@
       </c>
       <c r="F1374" t="inlineStr">
         <is>
-          <t>2026-08-04 23:14:59</t>
+          <t>2026-08-04 23:15:04</t>
         </is>
       </c>
     </row>
@@ -38900,7 +38900,7 @@
       </c>
       <c r="B1375" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23277-edicao-2799</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23272-edicao-2798</t>
         </is>
       </c>
       <c r="C1375" t="inlineStr">
@@ -38916,7 +38916,7 @@
       </c>
       <c r="F1375" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:04</t>
+          <t>2026-08-04 23:15:05</t>
         </is>
       </c>
     </row>
@@ -38944,7 +38944,7 @@
       </c>
       <c r="F1376" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:05</t>
+          <t>2026-08-04 23:15:10</t>
         </is>
       </c>
     </row>
@@ -38956,7 +38956,7 @@
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23272-edicao-2798</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23269-edicao-2797</t>
         </is>
       </c>
       <c r="C1377" t="inlineStr">
@@ -39000,7 +39000,7 @@
       </c>
       <c r="F1378" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:10</t>
+          <t>2026-08-04 23:15:15</t>
         </is>
       </c>
     </row>
@@ -39012,7 +39012,7 @@
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23269-edicao-2797</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23265-edicao-2796</t>
         </is>
       </c>
       <c r="C1379" t="inlineStr">
@@ -39028,7 +39028,7 @@
       </c>
       <c r="F1379" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:15</t>
+          <t>2026-08-04 23:15:16</t>
         </is>
       </c>
     </row>
@@ -39056,7 +39056,7 @@
       </c>
       <c r="F1380" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:16</t>
+          <t>2026-08-04 23:15:21</t>
         </is>
       </c>
     </row>
@@ -39068,7 +39068,7 @@
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23265-edicao-2796</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23258-edicao-2795</t>
         </is>
       </c>
       <c r="C1381" t="inlineStr">
@@ -39112,7 +39112,7 @@
       </c>
       <c r="F1382" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:21</t>
+          <t>2026-08-04 23:15:26</t>
         </is>
       </c>
     </row>
@@ -39124,7 +39124,7 @@
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23258-edicao-2795</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23249-edicao-2794</t>
         </is>
       </c>
       <c r="C1383" t="inlineStr">
@@ -39140,7 +39140,7 @@
       </c>
       <c r="F1383" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:26</t>
+          <t>2026-08-04 23:15:27</t>
         </is>
       </c>
     </row>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="F1384" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:27</t>
+          <t>2026-08-04 23:15:32</t>
         </is>
       </c>
     </row>
@@ -39180,7 +39180,7 @@
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23249-edicao-2794</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23237-edicao-2793</t>
         </is>
       </c>
       <c r="C1385" t="inlineStr">
@@ -39224,7 +39224,7 @@
       </c>
       <c r="F1386" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:32</t>
+          <t>2026-08-04 23:15:38</t>
         </is>
       </c>
     </row>
@@ -39236,7 +39236,7 @@
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23237-edicao-2793</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23226-edicao-2792</t>
         </is>
       </c>
       <c r="C1387" t="inlineStr">
@@ -39280,7 +39280,7 @@
       </c>
       <c r="F1388" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:38</t>
+          <t>2026-08-04 23:15:44</t>
         </is>
       </c>
     </row>
@@ -39292,7 +39292,7 @@
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23226-edicao-2792</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23221-edicao-2791</t>
         </is>
       </c>
       <c r="C1389" t="inlineStr">
@@ -39336,7 +39336,7 @@
       </c>
       <c r="F1390" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:44</t>
+          <t>2026-08-04 23:15:49</t>
         </is>
       </c>
     </row>
@@ -39348,7 +39348,7 @@
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial/23221-edicao-2791</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial?start=50</t>
         </is>
       </c>
       <c r="C1391" t="inlineStr">
@@ -39364,7 +39364,7 @@
       </c>
       <c r="F1391" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:49</t>
+          <t>2026-08-04 23:15:50</t>
         </is>
       </c>
     </row>
@@ -39392,7 +39392,7 @@
       </c>
       <c r="F1392" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:50</t>
+          <t>2026-08-04 23:15:55</t>
         </is>
       </c>
     </row>
@@ -39404,7 +39404,7 @@
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial?start=50</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial?start=100</t>
         </is>
       </c>
       <c r="C1393" t="inlineStr">
@@ -39420,7 +39420,7 @@
       </c>
       <c r="F1393" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:55</t>
+          <t>2026-08-04 23:15:56</t>
         </is>
       </c>
     </row>
@@ -39448,7 +39448,7 @@
       </c>
       <c r="F1394" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:56</t>
+          <t>2026-08-04 23:16:01</t>
         </is>
       </c>
     </row>
@@ -39460,7 +39460,7 @@
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial?start=100</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial?start=150</t>
         </is>
       </c>
       <c r="C1395" t="inlineStr">
@@ -39476,7 +39476,7 @@
       </c>
       <c r="F1395" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:01</t>
+          <t>2026-08-04 23:16:02</t>
         </is>
       </c>
     </row>
@@ -39504,7 +39504,7 @@
       </c>
       <c r="F1396" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:02</t>
+          <t>2026-08-04 23:16:07</t>
         </is>
       </c>
     </row>
@@ -39516,7 +39516,7 @@
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial?start=150</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial?start=200</t>
         </is>
       </c>
       <c r="C1397" t="inlineStr">
@@ -39532,7 +39532,7 @@
       </c>
       <c r="F1397" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:07</t>
+          <t>2026-08-04 23:16:08</t>
         </is>
       </c>
     </row>
@@ -39560,7 +39560,7 @@
       </c>
       <c r="F1398" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:08</t>
+          <t>2026-08-04 23:16:13</t>
         </is>
       </c>
     </row>
@@ -39572,7 +39572,7 @@
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial?start=200</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial?start=250</t>
         </is>
       </c>
       <c r="C1399" t="inlineStr">
@@ -39616,7 +39616,7 @@
       </c>
       <c r="F1400" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:13</t>
+          <t>2026-08-04 23:16:18</t>
         </is>
       </c>
     </row>
@@ -39628,7 +39628,7 @@
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial?start=250</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial?start=300</t>
         </is>
       </c>
       <c r="C1401" t="inlineStr">
@@ -39644,7 +39644,7 @@
       </c>
       <c r="F1401" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:18</t>
+          <t>2026-08-04 23:16:19</t>
         </is>
       </c>
     </row>
@@ -39672,7 +39672,7 @@
       </c>
       <c r="F1402" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:19</t>
+          <t>2026-08-04 23:16:24</t>
         </is>
       </c>
     </row>
@@ -39684,7 +39684,7 @@
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial?start=300</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial?start=350</t>
         </is>
       </c>
       <c r="C1403" t="inlineStr">
@@ -39728,7 +39728,7 @@
       </c>
       <c r="F1404" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:24</t>
+          <t>2026-08-04 23:16:29</t>
         </is>
       </c>
     </row>
@@ -39740,7 +39740,7 @@
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial?start=350</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial?start=400</t>
         </is>
       </c>
       <c r="C1405" t="inlineStr">
@@ -39756,7 +39756,7 @@
       </c>
       <c r="F1405" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:29</t>
+          <t>2026-08-04 23:16:30</t>
         </is>
       </c>
     </row>
@@ -39784,7 +39784,7 @@
       </c>
       <c r="F1406" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:30</t>
+          <t>2026-08-04 23:16:35</t>
         </is>
       </c>
     </row>
@@ -39796,7 +39796,7 @@
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial?start=400</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial?start=450</t>
         </is>
       </c>
       <c r="C1407" t="inlineStr">
@@ -39840,7 +39840,7 @@
       </c>
       <c r="F1408" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:35</t>
+          <t>2026-08-04 23:16:40</t>
         </is>
       </c>
     </row>
@@ -39852,7 +39852,7 @@
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial?start=450</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial?start=2750</t>
         </is>
       </c>
       <c r="C1409" t="inlineStr">
@@ -39868,7 +39868,7 @@
       </c>
       <c r="F1409" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:40</t>
+          <t>2026-08-04 23:16:41</t>
         </is>
       </c>
     </row>
@@ -39896,7 +39896,7 @@
       </c>
       <c r="F1410" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:41</t>
+          <t>2026-08-04 23:16:46</t>
         </is>
       </c>
     </row>
@@ -39908,7 +39908,7 @@
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/informacoes/boletim-oficial?start=2750</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/servicos/licitacao/credenciamentos/15992-credenciamento-de-clinicas-veterinarias-e-hospitais-veterinarios-2022?tmpl=component&amp;print=1</t>
         </is>
       </c>
       <c r="C1411" t="inlineStr">
@@ -39924,7 +39924,7 @@
       </c>
       <c r="F1411" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:46</t>
+          <t>2026-08-04 23:23:01</t>
         </is>
       </c>
     </row>
@@ -39952,7 +39952,7 @@
       </c>
       <c r="F1412" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:01</t>
+          <t>2026-08-04 23:23:06</t>
         </is>
       </c>
     </row>
@@ -39964,7 +39964,7 @@
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/servicos/licitacao/credenciamentos/15992-credenciamento-de-clinicas-veterinarias-e-hospitais-veterinarios-2022?tmpl=component&amp;print=1</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/component/mailto/?tmpl=component&amp;template=cloudbase3&amp;link=baf956ed46a15f2bd4f546a1ef0ee386dc1a1720</t>
         </is>
       </c>
       <c r="C1413" t="inlineStr">
@@ -39980,7 +39980,7 @@
       </c>
       <c r="F1413" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:06</t>
+          <t>2026-08-04 23:23:07</t>
         </is>
       </c>
     </row>
@@ -40008,7 +40008,7 @@
       </c>
       <c r="F1414" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:07</t>
+          <t>2026-08-04 23:23:12</t>
         </is>
       </c>
     </row>
@@ -40020,7 +40020,7 @@
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/component/mailto/?tmpl=component&amp;template=cloudbase3&amp;link=baf956ed46a15f2bd4f546a1ef0ee386dc1a1720</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/servicos/licitacao/credenciamentos/16344-credenciamento-para-prestacao-de-servicos-de-desenvolvimento-esportivo-cultural-e-recreativo-2022</t>
         </is>
       </c>
       <c r="C1415" t="inlineStr">
@@ -40064,7 +40064,7 @@
       </c>
       <c r="F1416" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:12</t>
+          <t>2026-08-04 23:23:18</t>
         </is>
       </c>
     </row>
@@ -40076,7 +40076,7 @@
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/servicos/licitacao/credenciamentos/16344-credenciamento-para-prestacao-de-servicos-de-desenvolvimento-esportivo-cultural-e-recreativo-2022</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/servicos/licitacao/credenciamentos/15981-subcomissao-tecnica-para-inscricao-de-profissionais-em-comunicacao-publicidade-ou-marketing</t>
         </is>
       </c>
       <c r="C1417" t="inlineStr">
@@ -40120,7 +40120,7 @@
       </c>
       <c r="F1418" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:18</t>
+          <t>2026-08-04 23:23:24</t>
         </is>
       </c>
     </row>
@@ -40132,7 +40132,7 @@
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/servicos/licitacao/credenciamentos/15981-subcomissao-tecnica-para-inscricao-de-profissionais-em-comunicacao-publicidade-ou-marketing</t>
+          <t>https://telemacoborba.pr.gov.br/servicos/licitacao/manuais-decretos/18738-e-book-regulamentacao-da-nova-lei-de-licitacoes.html</t>
         </is>
       </c>
       <c r="C1419" t="inlineStr">
@@ -40148,7 +40148,7 @@
       </c>
       <c r="F1419" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:24</t>
+          <t>2026-08-04 23:27:54</t>
         </is>
       </c>
     </row>
@@ -40176,7 +40176,7 @@
       </c>
       <c r="F1420" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:54</t>
+          <t>2026-08-04 23:27:59</t>
         </is>
       </c>
     </row>
@@ -40188,7 +40188,7 @@
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>https://telemacoborba.pr.gov.br/servicos/licitacao/manuais-decretos/18738-e-book-regulamentacao-da-nova-lei-de-licitacoes.html</t>
+          <t>https://telemacoborba.pr.gov.br/75-temp/10944-auxilio-emergencial-para-trabalhadores-da-cultura-encerra-dia-14-de-setembro.html</t>
         </is>
       </c>
       <c r="C1421" t="inlineStr">
@@ -40204,7 +40204,7 @@
       </c>
       <c r="F1421" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:59</t>
+          <t>2026-08-04 23:41:22</t>
         </is>
       </c>
     </row>
@@ -40232,7 +40232,7 @@
       </c>
       <c r="F1422" t="inlineStr">
         <is>
-          <t>2026-08-04 23:41:22</t>
+          <t>2026-08-04 23:41:27</t>
         </is>
       </c>
     </row>
@@ -40244,7 +40244,7 @@
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>https://telemacoborba.pr.gov.br/75-temp/10944-auxilio-emergencial-para-trabalhadores-da-cultura-encerra-dia-14-de-setembro.html</t>
+          <t>https://telemacoborba.pr.gov.br/75-temp/11285-trabalhadores-da-cultura-tem-ate-14-de-outubro-para-solicitar-auxilio-emergencial.html</t>
         </is>
       </c>
       <c r="C1423" t="inlineStr">
@@ -40260,7 +40260,7 @@
       </c>
       <c r="F1423" t="inlineStr">
         <is>
-          <t>2026-08-04 23:41:27</t>
+          <t>2026-08-04 23:41:28</t>
         </is>
       </c>
     </row>
@@ -40288,7 +40288,7 @@
       </c>
       <c r="F1424" t="inlineStr">
         <is>
-          <t>2026-08-04 23:41:28</t>
+          <t>2026-08-04 23:41:34</t>
         </is>
       </c>
     </row>
@@ -40300,7 +40300,7 @@
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>https://telemacoborba.pr.gov.br/75-temp/11285-trabalhadores-da-cultura-tem-ate-14-de-outubro-para-solicitar-auxilio-emergencial.html</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/imprensa/noticias/70-coronavirus</t>
         </is>
       </c>
       <c r="C1425" t="inlineStr">
@@ -40316,7 +40316,7 @@
       </c>
       <c r="F1425" t="inlineStr">
         <is>
-          <t>2026-08-04 23:41:34</t>
+          <t>2026-08-05 00:38:48</t>
         </is>
       </c>
     </row>
@@ -40344,7 +40344,7 @@
       </c>
       <c r="F1426" t="inlineStr">
         <is>
-          <t>2026-08-05 00:38:48</t>
+          <t>2026-08-05 00:38:53</t>
         </is>
       </c>
     </row>
@@ -40356,7 +40356,7 @@
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/imprensa/noticias/70-coronavirus</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/imprensa/noticias/70-coronavirus/12635-legislacao-covid-19?tmpl=component&amp;print=1&amp;layout=default</t>
         </is>
       </c>
       <c r="C1427" t="inlineStr">
@@ -40400,7 +40400,7 @@
       </c>
       <c r="F1428" t="inlineStr">
         <is>
-          <t>2026-08-05 00:38:53</t>
+          <t>2026-08-05 00:38:59</t>
         </is>
       </c>
     </row>
@@ -40412,7 +40412,7 @@
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/imprensa/noticias/70-coronavirus/12635-legislacao-covid-19?tmpl=component&amp;print=1&amp;layout=default</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/component/mailto/?tmpl=component&amp;template=cloudbase3&amp;link=000866116369437657507ff15e5ce8d99c6fb32b</t>
         </is>
       </c>
       <c r="C1429" t="inlineStr">
@@ -40456,7 +40456,7 @@
       </c>
       <c r="F1430" t="inlineStr">
         <is>
-          <t>2026-08-05 00:38:59</t>
+          <t>2026-08-05 00:39:04</t>
         </is>
       </c>
     </row>
@@ -40468,7 +40468,7 @@
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/component/mailto/?tmpl=component&amp;template=cloudbase3&amp;link=000866116369437657507ff15e5ce8d99c6fb32b</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/imprensa/noticias/70-coronavirus/13182-vacinas-contra-a-covid-19</t>
         </is>
       </c>
       <c r="C1431" t="inlineStr">
@@ -40484,7 +40484,7 @@
       </c>
       <c r="F1431" t="inlineStr">
         <is>
-          <t>2026-08-05 00:39:04</t>
+          <t>2026-08-05 00:39:05</t>
         </is>
       </c>
     </row>
@@ -40512,7 +40512,7 @@
       </c>
       <c r="F1432" t="inlineStr">
         <is>
-          <t>2026-08-05 00:39:05</t>
+          <t>2026-08-05 00:39:10</t>
         </is>
       </c>
     </row>
@@ -40524,7 +40524,7 @@
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/imprensa/noticias/70-coronavirus/13182-vacinas-contra-a-covid-19</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/imprensa/noticias/70-coronavirus/11617-covid-19-rastreamento-de-contatos-de-suspeitos-comeca-na-segunda-23</t>
         </is>
       </c>
       <c r="C1433" t="inlineStr">
@@ -40568,7 +40568,7 @@
       </c>
       <c r="F1434" t="inlineStr">
         <is>
-          <t>2026-08-05 00:39:10</t>
+          <t>2026-08-05 00:39:15</t>
         </is>
       </c>
     </row>
@@ -40580,7 +40580,7 @@
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/imprensa/noticias/70-coronavirus/11617-covid-19-rastreamento-de-contatos-de-suspeitos-comeca-na-segunda-23</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/req-cancelamento-nfs-e?tmpl=component&amp;print=1</t>
         </is>
       </c>
       <c r="C1435" t="inlineStr">
@@ -40592,11 +40592,11 @@
         <v>404</v>
       </c>
       <c r="E1435" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1435" t="inlineStr">
         <is>
-          <t>2026-08-05 00:39:15</t>
+          <t>2026-08-05 00:49:45</t>
         </is>
       </c>
     </row>
@@ -40624,7 +40624,7 @@
       </c>
       <c r="F1436" t="inlineStr">
         <is>
-          <t>2026-08-05 00:49:45</t>
+          <t>2026-08-05 00:49:50</t>
         </is>
       </c>
     </row>
@@ -40636,7 +40636,7 @@
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/req-cancelamento-nfs-e?tmpl=component&amp;print=1</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/component/mailto/?tmpl=component&amp;template=cloudbase3&amp;link=2347cf3d18372266a2ccde092e5c9fa7eb5c43da</t>
         </is>
       </c>
       <c r="C1437" t="inlineStr">
@@ -40680,7 +40680,7 @@
       </c>
       <c r="F1438" t="inlineStr">
         <is>
-          <t>2026-08-05 00:49:50</t>
+          <t>2026-08-05 00:49:56</t>
         </is>
       </c>
     </row>
@@ -40692,7 +40692,7 @@
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/component/mailto/?tmpl=component&amp;template=cloudbase3&amp;link=2347cf3d18372266a2ccde092e5c9fa7eb5c43da</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/decreto-26-199</t>
         </is>
       </c>
       <c r="C1439" t="inlineStr">
@@ -40736,7 +40736,7 @@
       </c>
       <c r="F1440" t="inlineStr">
         <is>
-          <t>2026-08-05 00:49:56</t>
+          <t>2026-08-05 00:50:01</t>
         </is>
       </c>
     </row>
@@ -40748,7 +40748,7 @@
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/decreto-26-199</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/lei-complementar-059-2019</t>
         </is>
       </c>
       <c r="C1441" t="inlineStr">
@@ -40792,7 +40792,7 @@
       </c>
       <c r="F1442" t="inlineStr">
         <is>
-          <t>2026-08-05 00:50:01</t>
+          <t>2026-08-05 00:50:06</t>
         </is>
       </c>
     </row>
@@ -40804,7 +40804,7 @@
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/lei-complementar-059-2019</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/lei-1190-1998</t>
         </is>
       </c>
       <c r="C1443" t="inlineStr">
@@ -40820,7 +40820,7 @@
       </c>
       <c r="F1443" t="inlineStr">
         <is>
-          <t>2026-08-05 00:50:06</t>
+          <t>2026-08-05 00:50:07</t>
         </is>
       </c>
     </row>
@@ -40848,7 +40848,7 @@
       </c>
       <c r="F1444" t="inlineStr">
         <is>
-          <t>2026-08-05 00:50:07</t>
+          <t>2026-08-05 00:50:12</t>
         </is>
       </c>
     </row>
@@ -40860,7 +40860,7 @@
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/lei-1190-1998</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/lei-1425-2003</t>
         </is>
       </c>
       <c r="C1445" t="inlineStr">
@@ -40876,7 +40876,7 @@
       </c>
       <c r="F1445" t="inlineStr">
         <is>
-          <t>2026-08-05 00:50:12</t>
+          <t>2026-08-05 00:50:13</t>
         </is>
       </c>
     </row>
@@ -40904,7 +40904,7 @@
       </c>
       <c r="F1446" t="inlineStr">
         <is>
-          <t>2026-08-05 00:50:13</t>
+          <t>2026-08-05 00:50:18</t>
         </is>
       </c>
     </row>
@@ -40916,7 +40916,7 @@
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/lei-1425-2003</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/lei-1719</t>
         </is>
       </c>
       <c r="C1447" t="inlineStr">
@@ -40960,7 +40960,7 @@
       </c>
       <c r="F1448" t="inlineStr">
         <is>
-          <t>2026-08-05 00:50:18</t>
+          <t>2026-08-05 00:50:23</t>
         </is>
       </c>
     </row>
@@ -40972,7 +40972,7 @@
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/lei-1719</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/lei-1489</t>
         </is>
       </c>
       <c r="C1449" t="inlineStr">
@@ -40988,7 +40988,7 @@
       </c>
       <c r="F1449" t="inlineStr">
         <is>
-          <t>2026-08-05 00:50:23</t>
+          <t>2026-08-05 00:50:24</t>
         </is>
       </c>
     </row>
@@ -41016,7 +41016,7 @@
       </c>
       <c r="F1450" t="inlineStr">
         <is>
-          <t>2026-08-05 00:50:24</t>
+          <t>2026-08-05 00:50:29</t>
         </is>
       </c>
     </row>
@@ -41028,7 +41028,7 @@
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/lei-1489</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/decreto-21-018</t>
         </is>
       </c>
       <c r="C1451" t="inlineStr">
@@ -41044,7 +41044,7 @@
       </c>
       <c r="F1451" t="inlineStr">
         <is>
-          <t>2026-08-05 00:50:29</t>
+          <t>2026-08-05 00:50:30</t>
         </is>
       </c>
     </row>
@@ -41072,7 +41072,7 @@
       </c>
       <c r="F1452" t="inlineStr">
         <is>
-          <t>2026-08-05 00:50:30</t>
+          <t>2026-08-05 00:50:34</t>
         </is>
       </c>
     </row>
@@ -41084,7 +41084,7 @@
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/decreto-21-018</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/lei-29</t>
         </is>
       </c>
       <c r="C1453" t="inlineStr">
@@ -41100,7 +41100,7 @@
       </c>
       <c r="F1453" t="inlineStr">
         <is>
-          <t>2026-08-05 00:50:34</t>
+          <t>2026-08-05 00:50:35</t>
         </is>
       </c>
     </row>
@@ -41128,7 +41128,7 @@
       </c>
       <c r="F1454" t="inlineStr">
         <is>
-          <t>2026-08-05 00:50:35</t>
+          <t>2026-08-05 00:50:40</t>
         </is>
       </c>
     </row>
@@ -41140,7 +41140,7 @@
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/lei-29</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/lei-complementar-44-2018</t>
         </is>
       </c>
       <c r="C1455" t="inlineStr">
@@ -41184,7 +41184,7 @@
       </c>
       <c r="F1456" t="inlineStr">
         <is>
-          <t>2026-08-05 00:50:40</t>
+          <t>2026-08-05 00:50:46</t>
         </is>
       </c>
     </row>
@@ -41196,7 +41196,7 @@
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/lei-complementar-44-2018</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/decreto-19679-nota-fiscal-eletronica</t>
         </is>
       </c>
       <c r="C1457" t="inlineStr">
@@ -41240,7 +41240,7 @@
       </c>
       <c r="F1458" t="inlineStr">
         <is>
-          <t>2026-08-05 00:50:46</t>
+          <t>2026-08-05 00:50:51</t>
         </is>
       </c>
     </row>
@@ -41252,7 +41252,7 @@
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/decreto-19679-nota-fiscal-eletronica</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/req-cancelamento-nfs-e</t>
         </is>
       </c>
       <c r="C1459" t="inlineStr">
@@ -41268,7 +41268,7 @@
       </c>
       <c r="F1459" t="inlineStr">
         <is>
-          <t>2026-08-05 00:50:51</t>
+          <t>2026-08-05 00:50:52</t>
         </is>
       </c>
     </row>
@@ -41296,7 +41296,7 @@
       </c>
       <c r="F1460" t="inlineStr">
         <is>
-          <t>2026-08-05 00:50:52</t>
+          <t>2026-08-05 00:50:57</t>
         </is>
       </c>
     </row>
@@ -41308,7 +41308,7 @@
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/req-cancelamento-nfs-e</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/decreto-26-222</t>
         </is>
       </c>
       <c r="C1461" t="inlineStr">
@@ -41352,7 +41352,7 @@
       </c>
       <c r="F1462" t="inlineStr">
         <is>
-          <t>2026-08-05 00:50:57</t>
+          <t>2026-08-05 00:51:02</t>
         </is>
       </c>
     </row>
@@ -41364,7 +41364,7 @@
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/decreto-26-222</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/decreto-26-022</t>
         </is>
       </c>
       <c r="C1463" t="inlineStr">
@@ -41380,7 +41380,7 @@
       </c>
       <c r="F1463" t="inlineStr">
         <is>
-          <t>2026-08-05 00:51:02</t>
+          <t>2026-08-05 00:51:03</t>
         </is>
       </c>
     </row>
@@ -41408,7 +41408,7 @@
       </c>
       <c r="F1464" t="inlineStr">
         <is>
-          <t>2026-08-05 00:51:03</t>
+          <t>2026-08-05 00:51:08</t>
         </is>
       </c>
     </row>
@@ -41420,7 +41420,7 @@
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/decreto-26-022</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/lei-complementar-068-2019</t>
         </is>
       </c>
       <c r="C1465" t="inlineStr">
@@ -41464,7 +41464,7 @@
       </c>
       <c r="F1466" t="inlineStr">
         <is>
-          <t>2026-08-05 00:51:08</t>
+          <t>2026-08-05 00:51:13</t>
         </is>
       </c>
     </row>
@@ -41476,7 +41476,7 @@
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/lei-complementar-068-2019</t>
+          <t>http://www.telemacoborba.pr.gov.br/index.php/decreto-26-378-2020</t>
         </is>
       </c>
       <c r="C1467" t="inlineStr">
@@ -41492,7 +41492,7 @@
       </c>
       <c r="F1467" t="inlineStr">
         <is>
-          <t>2026-08-05 00:51:13</t>
+          <t>2026-08-05 00:51:14</t>
         </is>
       </c>
     </row>
@@ -41520,7 +41520,7 @@
       </c>
       <c r="F1468" t="inlineStr">
         <is>
-          <t>2026-08-05 00:51:14</t>
+          <t>2026-08-05 00:51:20</t>
         </is>
       </c>
     </row>
@@ -41532,23 +41532,23 @@
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>http://www.telemacoborba.pr.gov.br/index.php/decreto-26-378-2020</t>
+          <t>https://telemacoborba.pr.gov.br/index.php/servicos/guia-de-servicos/obituario/18604-falecimentos-do-dia-16-06-2023?tmpl=component&amp;print=1</t>
         </is>
       </c>
       <c r="C1469" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_521</t>
         </is>
       </c>
       <c r="D1469" t="n">
-        <v>404</v>
+        <v>521</v>
       </c>
       <c r="E1469" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F1469" t="inlineStr">
         <is>
-          <t>2026-08-05 00:51:20</t>
+          <t>2026-08-07 14:58:52</t>
         </is>
       </c>
     </row>
@@ -41560,23 +41560,23 @@
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>https://telemacoborba.pr.gov.br/index.php/servicos/guia-de-servicos/obituario/18604-falecimentos-do-dia-16-06-2023?tmpl=component&amp;print=1</t>
+          <t>https://telemacoborba.pr.gov.br/index.php/component/mailto/?tmpl=component&amp;template=cloudbase3&amp;link=dea2b9deafd401109e04b1e472155f13b66d1c31</t>
         </is>
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>HTTP_520</t>
+          <t>HTTP_521</t>
         </is>
       </c>
       <c r="D1470" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E1470" t="n">
         <v>9</v>
       </c>
       <c r="F1470" t="inlineStr">
         <is>
-          <t>2026-08-07 14:58:47</t>
+          <t>2026-08-07 14:58:58</t>
         </is>
       </c>
     </row>
@@ -41588,23 +41588,23 @@
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>https://telemacoborba.pr.gov.br/index.php/servicos/guia-de-servicos/obituario/18604-falecimentos-do-dia-16-06-2023?tmpl=component&amp;print=1</t>
+          <t>https://telemacoborba.pr.gov.br/index.php/servicos/guia-de-servicos/obituario/18601-falecimentos-do-dia-13-06-2023?tmpl=component&amp;print=1</t>
         </is>
       </c>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>HTTP_521</t>
+          <t>HTTP_502</t>
         </is>
       </c>
       <c r="D1471" t="n">
-        <v>521</v>
+        <v>502</v>
       </c>
       <c r="E1471" t="n">
         <v>9</v>
       </c>
       <c r="F1471" t="inlineStr">
         <is>
-          <t>2026-08-07 14:58:52</t>
+          <t>2026-08-07 14:59:03</t>
         </is>
       </c>
     </row>
@@ -41616,23 +41616,23 @@
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>https://telemacoborba.pr.gov.br/index.php/component/mailto/?tmpl=component&amp;template=cloudbase3&amp;link=dea2b9deafd401109e04b1e472155f13b66d1c31</t>
+          <t>https://telemacoborba.pr.gov.br/informacoes/pss/pss-2021.html</t>
         </is>
       </c>
       <c r="C1472" t="inlineStr">
         <is>
-          <t>HTTP_521</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D1472" t="n">
-        <v>521</v>
+        <v>404</v>
       </c>
       <c r="E1472" t="n">
         <v>9</v>
       </c>
       <c r="F1472" t="inlineStr">
         <is>
-          <t>2026-08-07 14:58:52</t>
+          <t>2026-08-07 16:30:43</t>
         </is>
       </c>
     </row>
@@ -41644,23 +41644,23 @@
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>https://telemacoborba.pr.gov.br/index.php/component/mailto/?tmpl=component&amp;template=cloudbase3&amp;link=dea2b9deafd401109e04b1e472155f13b66d1c31</t>
+          <t>https://telemacoborba.pr.gov.br/informacoes/pss/pss-2021.html</t>
         </is>
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>HTTP_521</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D1473" t="n">
-        <v>521</v>
+        <v>404</v>
       </c>
       <c r="E1473" t="n">
         <v>9</v>
       </c>
       <c r="F1473" t="inlineStr">
         <is>
-          <t>2026-08-07 14:58:58</t>
+          <t>2026-08-07 16:30:49</t>
         </is>
       </c>
     </row>
@@ -41672,23 +41672,23 @@
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>https://telemacoborba.pr.gov.br/index.php/servicos/guia-de-servicos/obituario/18601-falecimentos-do-dia-13-06-2023?tmpl=component&amp;print=1</t>
+          <t>https://telemacoborba.pr.gov.br/informacoes/pss/pss-2020.html</t>
         </is>
       </c>
       <c r="C1474" t="inlineStr">
         <is>
-          <t>HTTP_521</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D1474" t="n">
-        <v>521</v>
+        <v>404</v>
       </c>
       <c r="E1474" t="n">
         <v>9</v>
       </c>
       <c r="F1474" t="inlineStr">
         <is>
-          <t>2026-08-07 14:58:58</t>
+          <t>2026-08-07 16:37:31</t>
         </is>
       </c>
     </row>
@@ -41700,23 +41700,79 @@
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>https://telemacoborba.pr.gov.br/index.php/servicos/guia-de-servicos/obituario/18601-falecimentos-do-dia-13-06-2023?tmpl=component&amp;print=1</t>
+          <t>https://telemacoborba.pr.gov.br/informacoes/pss/pss-2020.html</t>
         </is>
       </c>
       <c r="C1475" t="inlineStr">
         <is>
-          <t>HTTP_502</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D1475" t="n">
-        <v>502</v>
+        <v>404</v>
       </c>
       <c r="E1475" t="n">
         <v>9</v>
       </c>
       <c r="F1475" t="inlineStr">
         <is>
-          <t>2026-08-07 14:59:03</t>
+          <t>2026-08-07 16:37:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/melhoramigo</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D1476" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1476" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1476" t="inlineStr">
+        <is>
+          <t>2026-08-07 17:39:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/melhoramigo</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D1477" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1477" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1477" t="inlineStr">
+        <is>
+          <t>2026-08-07 17:41:32</t>
         </is>
       </c>
     </row>
